--- a/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_VRES.xlsx
+++ b/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_VRES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\LEGO-Pyomo\data\Fertig - 1.a_MS_misch_base\1.a_MS_misch_grid-reduced\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tom\Tu Graz\Masterarbeit\Git\LEGO-Pyomo\data\Fertig - 1.a_MS_misch_base\1.a_MS_misch_grid-reduced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62B107D-2847-4C5A-8E00-A4D7EE5A5AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBABF25D-0E06-4455-A906-0E562FC924AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34450" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -338,9 +338,6 @@
     <t>Solar</t>
   </si>
   <si>
-    <t>kn002</t>
-  </si>
-  <si>
     <t>Dyler 2.0_MS_misch</t>
   </si>
   <si>
@@ -350,9 +347,6 @@
     <t>PV_006</t>
   </si>
   <si>
-    <t>kn006</t>
-  </si>
-  <si>
     <t>RoR_006</t>
   </si>
   <si>
@@ -840,6 +834,12 @@
   </si>
   <si>
     <t>kn296</t>
+  </si>
+  <si>
+    <t>kn002_IN</t>
+  </si>
+  <si>
+    <t>kn006_IN</t>
   </si>
 </sst>
 </file>
@@ -1293,17 +1293,17 @@
     <tabColor rgb="FF008080"/>
   </sheetPr>
   <dimension ref="A1:U94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5859375" customWidth="1"/>
-    <col min="2" max="2" width="19.703125" customWidth="1"/>
-    <col min="3" max="15" width="15.703125" customWidth="1"/>
-    <col min="16" max="17" width="20.1171875" customWidth="1"/>
-    <col min="18" max="19" width="15.703125" customWidth="1"/>
-    <col min="20" max="21" width="24.5859375" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="17" width="20.109375" customWidth="1"/>
+    <col min="18" max="19" width="15.6640625" customWidth="1"/>
+    <col min="20" max="21" width="24.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1328,7 +1328,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>24</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>35</v>
@@ -1529,7 +1529,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
         <v>53</v>
@@ -1592,7 +1592,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
         <v>56</v>
@@ -1655,7 +1655,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
@@ -1665,7 +1665,7 @@
         <v>73</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>74</v>
+        <v>240</v>
       </c>
       <c r="F8" s="13">
         <v>1</v>
@@ -1702,23 +1702,23 @@
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
       <c r="T8" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U8" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="F9" s="13">
         <v>1</v>
@@ -1755,23 +1755,23 @@
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
       <c r="T9" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U9" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="F10" s="13">
         <v>1</v>
@@ -1808,23 +1808,23 @@
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
       <c r="T10" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U10" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F11" s="13">
         <v>1</v>
@@ -1861,23 +1861,23 @@
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
       <c r="T11" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U11" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F12" s="13">
         <v>1</v>
@@ -1914,23 +1914,23 @@
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
       <c r="T12" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U12" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F13" s="13">
         <v>1</v>
@@ -1967,23 +1967,23 @@
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
       <c r="T13" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U13" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F14" s="13">
         <v>1</v>
@@ -2020,23 +2020,23 @@
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
       <c r="T14" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U14" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F15" s="13">
         <v>1</v>
@@ -2073,23 +2073,23 @@
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
       <c r="T15" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U15" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F16" s="13">
         <v>1</v>
@@ -2126,23 +2126,23 @@
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
       <c r="T16" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U16" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F17" s="13">
         <v>1</v>
@@ -2179,23 +2179,23 @@
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
       <c r="T17" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U17" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F18" s="13">
         <v>1</v>
@@ -2232,23 +2232,23 @@
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
       <c r="T18" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U18" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F19" s="13">
         <v>1</v>
@@ -2285,23 +2285,23 @@
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
       <c r="T19" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U19" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F20" s="13">
         <v>1</v>
@@ -2338,23 +2338,23 @@
       <c r="R20" s="17"/>
       <c r="S20" s="17"/>
       <c r="T20" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U20" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F21" s="13">
         <v>1</v>
@@ -2391,23 +2391,23 @@
       <c r="R21" s="17"/>
       <c r="S21" s="17"/>
       <c r="T21" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U21" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F22" s="13">
         <v>1</v>
@@ -2444,23 +2444,23 @@
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
       <c r="T22" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U22" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F23" s="13">
         <v>1</v>
@@ -2497,23 +2497,23 @@
       <c r="R23" s="17"/>
       <c r="S23" s="17"/>
       <c r="T23" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U23" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F24" s="13">
         <v>1</v>
@@ -2550,23 +2550,23 @@
       <c r="R24" s="17"/>
       <c r="S24" s="17"/>
       <c r="T24" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U24" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F25" s="13">
         <v>1</v>
@@ -2603,23 +2603,23 @@
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
       <c r="T25" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U25" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F26" s="13">
         <v>1</v>
@@ -2656,23 +2656,23 @@
       <c r="R26" s="17"/>
       <c r="S26" s="17"/>
       <c r="T26" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U26" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F27" s="13">
         <v>1</v>
@@ -2709,23 +2709,23 @@
       <c r="R27" s="17"/>
       <c r="S27" s="17"/>
       <c r="T27" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U27" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F28" s="13">
         <v>1</v>
@@ -2762,23 +2762,23 @@
       <c r="R28" s="17"/>
       <c r="S28" s="17"/>
       <c r="T28" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U28" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F29" s="13">
         <v>1</v>
@@ -2815,23 +2815,23 @@
       <c r="R29" s="17"/>
       <c r="S29" s="17"/>
       <c r="T29" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U29" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F30" s="13">
         <v>1</v>
@@ -2868,23 +2868,23 @@
       <c r="R30" s="17"/>
       <c r="S30" s="17"/>
       <c r="T30" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U30" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F31" s="13">
         <v>1</v>
@@ -2921,23 +2921,23 @@
       <c r="R31" s="17"/>
       <c r="S31" s="17"/>
       <c r="T31" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U31" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F32" s="13">
         <v>1</v>
@@ -2974,23 +2974,23 @@
       <c r="R32" s="17"/>
       <c r="S32" s="17"/>
       <c r="T32" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U32" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F33" s="13">
         <v>1</v>
@@ -3027,23 +3027,23 @@
       <c r="R33" s="17"/>
       <c r="S33" s="17"/>
       <c r="T33" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U33" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F34" s="13">
         <v>1</v>
@@ -3080,23 +3080,23 @@
       <c r="R34" s="17"/>
       <c r="S34" s="17"/>
       <c r="T34" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U34" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F35" s="13">
         <v>1</v>
@@ -3133,23 +3133,23 @@
       <c r="R35" s="17"/>
       <c r="S35" s="17"/>
       <c r="T35" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U35" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F36" s="13">
         <v>1</v>
@@ -3186,23 +3186,23 @@
       <c r="R36" s="17"/>
       <c r="S36" s="17"/>
       <c r="T36" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U36" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D37" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F37" s="13">
         <v>1</v>
@@ -3239,23 +3239,23 @@
       <c r="R37" s="17"/>
       <c r="S37" s="17"/>
       <c r="T37" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U37" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F38" s="13">
         <v>1</v>
@@ -3292,23 +3292,23 @@
       <c r="R38" s="17"/>
       <c r="S38" s="17"/>
       <c r="T38" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U38" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F39" s="13">
         <v>1</v>
@@ -3345,23 +3345,23 @@
       <c r="R39" s="17"/>
       <c r="S39" s="17"/>
       <c r="T39" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U39" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D40" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F40" s="13">
         <v>1</v>
@@ -3398,23 +3398,23 @@
       <c r="R40" s="17"/>
       <c r="S40" s="17"/>
       <c r="T40" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U40" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="10"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D41" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F41" s="13">
         <v>1</v>
@@ -3451,23 +3451,23 @@
       <c r="R41" s="17"/>
       <c r="S41" s="17"/>
       <c r="T41" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U41" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="10"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F42" s="13">
         <v>1</v>
@@ -3504,23 +3504,23 @@
       <c r="R42" s="17"/>
       <c r="S42" s="17"/>
       <c r="T42" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U42" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F43" s="13">
         <v>1</v>
@@ -3557,23 +3557,23 @@
       <c r="R43" s="17"/>
       <c r="S43" s="17"/>
       <c r="T43" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U43" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F44" s="13">
         <v>1</v>
@@ -3610,23 +3610,23 @@
       <c r="R44" s="17"/>
       <c r="S44" s="17"/>
       <c r="T44" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U44" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F45" s="13">
         <v>1</v>
@@ -3663,23 +3663,23 @@
       <c r="R45" s="17"/>
       <c r="S45" s="17"/>
       <c r="T45" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U45" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D46" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F46" s="13">
         <v>1</v>
@@ -3716,23 +3716,23 @@
       <c r="R46" s="17"/>
       <c r="S46" s="17"/>
       <c r="T46" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U46" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F47" s="13">
         <v>1</v>
@@ -3769,23 +3769,23 @@
       <c r="R47" s="17"/>
       <c r="S47" s="17"/>
       <c r="T47" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U47" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D48" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F48" s="13">
         <v>1</v>
@@ -3822,23 +3822,23 @@
       <c r="R48" s="17"/>
       <c r="S48" s="17"/>
       <c r="T48" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U48" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F49" s="13">
         <v>1</v>
@@ -3875,23 +3875,23 @@
       <c r="R49" s="17"/>
       <c r="S49" s="17"/>
       <c r="T49" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U49" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" s="10"/>
       <c r="B50" s="11"/>
       <c r="C50" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F50" s="13">
         <v>1</v>
@@ -3928,23 +3928,23 @@
       <c r="R50" s="17"/>
       <c r="S50" s="17"/>
       <c r="T50" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U50" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
       <c r="B51" s="11"/>
       <c r="C51" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F51" s="13">
         <v>1</v>
@@ -3981,23 +3981,23 @@
       <c r="R51" s="17"/>
       <c r="S51" s="17"/>
       <c r="T51" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U51" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
       <c r="B52" s="11"/>
       <c r="C52" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F52" s="13">
         <v>1</v>
@@ -4034,23 +4034,23 @@
       <c r="R52" s="17"/>
       <c r="S52" s="17"/>
       <c r="T52" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U52" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" s="10"/>
       <c r="B53" s="11"/>
       <c r="C53" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F53" s="13">
         <v>1</v>
@@ -4087,23 +4087,23 @@
       <c r="R53" s="17"/>
       <c r="S53" s="17"/>
       <c r="T53" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U53" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" s="10"/>
       <c r="B54" s="11"/>
       <c r="C54" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F54" s="13">
         <v>1</v>
@@ -4140,23 +4140,23 @@
       <c r="R54" s="17"/>
       <c r="S54" s="17"/>
       <c r="T54" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U54" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="10"/>
       <c r="B55" s="11"/>
       <c r="C55" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F55" s="13">
         <v>1</v>
@@ -4193,23 +4193,23 @@
       <c r="R55" s="17"/>
       <c r="S55" s="17"/>
       <c r="T55" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U55" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="10"/>
       <c r="B56" s="11"/>
       <c r="C56" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D56" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F56" s="13">
         <v>1</v>
@@ -4246,23 +4246,23 @@
       <c r="R56" s="17"/>
       <c r="S56" s="17"/>
       <c r="T56" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U56" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="10"/>
       <c r="B57" s="11"/>
       <c r="C57" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D57" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F57" s="13">
         <v>1</v>
@@ -4299,23 +4299,23 @@
       <c r="R57" s="17"/>
       <c r="S57" s="17"/>
       <c r="T57" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U57" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
       <c r="B58" s="11"/>
       <c r="C58" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D58" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F58" s="13">
         <v>1</v>
@@ -4352,23 +4352,23 @@
       <c r="R58" s="17"/>
       <c r="S58" s="17"/>
       <c r="T58" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U58" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" s="10"/>
       <c r="B59" s="11"/>
       <c r="C59" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F59" s="13">
         <v>1</v>
@@ -4405,23 +4405,23 @@
       <c r="R59" s="17"/>
       <c r="S59" s="17"/>
       <c r="T59" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U59" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" s="10"/>
       <c r="B60" s="11"/>
       <c r="C60" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F60" s="13">
         <v>1</v>
@@ -4458,23 +4458,23 @@
       <c r="R60" s="17"/>
       <c r="S60" s="17"/>
       <c r="T60" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U60" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" s="10"/>
       <c r="B61" s="11"/>
       <c r="C61" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F61" s="13">
         <v>1</v>
@@ -4511,23 +4511,23 @@
       <c r="R61" s="17"/>
       <c r="S61" s="17"/>
       <c r="T61" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U61" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="11"/>
       <c r="C62" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D62" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F62" s="13">
         <v>1</v>
@@ -4564,23 +4564,23 @@
       <c r="R62" s="17"/>
       <c r="S62" s="17"/>
       <c r="T62" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U62" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="11"/>
       <c r="C63" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D63" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F63" s="13">
         <v>1</v>
@@ -4617,23 +4617,23 @@
       <c r="R63" s="17"/>
       <c r="S63" s="17"/>
       <c r="T63" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U63" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="11"/>
       <c r="C64" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F64" s="13">
         <v>1</v>
@@ -4670,23 +4670,23 @@
       <c r="R64" s="17"/>
       <c r="S64" s="17"/>
       <c r="T64" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U64" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="11"/>
       <c r="C65" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D65" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F65" s="13">
         <v>1</v>
@@ -4723,23 +4723,23 @@
       <c r="R65" s="17"/>
       <c r="S65" s="17"/>
       <c r="T65" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U65" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" s="10"/>
       <c r="B66" s="11"/>
       <c r="C66" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F66" s="13">
         <v>1</v>
@@ -4776,23 +4776,23 @@
       <c r="R66" s="17"/>
       <c r="S66" s="17"/>
       <c r="T66" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U66" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="11"/>
       <c r="C67" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F67" s="13">
         <v>1</v>
@@ -4829,23 +4829,23 @@
       <c r="R67" s="17"/>
       <c r="S67" s="17"/>
       <c r="T67" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U67" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="11"/>
       <c r="C68" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F68" s="13">
         <v>1</v>
@@ -4882,23 +4882,23 @@
       <c r="R68" s="17"/>
       <c r="S68" s="17"/>
       <c r="T68" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U68" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="11"/>
       <c r="C69" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D69" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F69" s="13">
         <v>1</v>
@@ -4935,23 +4935,23 @@
       <c r="R69" s="17"/>
       <c r="S69" s="17"/>
       <c r="T69" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U69" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="11"/>
       <c r="C70" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D70" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F70" s="13">
         <v>1</v>
@@ -4988,23 +4988,23 @@
       <c r="R70" s="17"/>
       <c r="S70" s="17"/>
       <c r="T70" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U70" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="11"/>
       <c r="C71" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D71" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F71" s="13">
         <v>1</v>
@@ -5041,23 +5041,23 @@
       <c r="R71" s="17"/>
       <c r="S71" s="17"/>
       <c r="T71" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U71" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="11"/>
       <c r="C72" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D72" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F72" s="13">
         <v>1</v>
@@ -5094,23 +5094,23 @@
       <c r="R72" s="17"/>
       <c r="S72" s="17"/>
       <c r="T72" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U72" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" s="10"/>
       <c r="B73" s="11"/>
       <c r="C73" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D73" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F73" s="13">
         <v>1</v>
@@ -5147,23 +5147,23 @@
       <c r="R73" s="17"/>
       <c r="S73" s="17"/>
       <c r="T73" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U73" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" s="10"/>
       <c r="B74" s="11"/>
       <c r="C74" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F74" s="13">
         <v>1</v>
@@ -5200,23 +5200,23 @@
       <c r="R74" s="17"/>
       <c r="S74" s="17"/>
       <c r="T74" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U74" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="11"/>
       <c r="C75" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D75" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F75" s="13">
         <v>1</v>
@@ -5253,23 +5253,23 @@
       <c r="R75" s="17"/>
       <c r="S75" s="17"/>
       <c r="T75" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U75" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
       <c r="B76" s="11"/>
       <c r="C76" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D76" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F76" s="13">
         <v>1</v>
@@ -5306,23 +5306,23 @@
       <c r="R76" s="17"/>
       <c r="S76" s="17"/>
       <c r="T76" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U76" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" s="10"/>
       <c r="B77" s="11"/>
       <c r="C77" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D77" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F77" s="13">
         <v>1</v>
@@ -5359,23 +5359,23 @@
       <c r="R77" s="17"/>
       <c r="S77" s="17"/>
       <c r="T77" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U77" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" s="10"/>
       <c r="B78" s="11"/>
       <c r="C78" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D78" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F78" s="13">
         <v>1</v>
@@ -5412,23 +5412,23 @@
       <c r="R78" s="17"/>
       <c r="S78" s="17"/>
       <c r="T78" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U78" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" s="10"/>
       <c r="B79" s="11"/>
       <c r="C79" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D79" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F79" s="13">
         <v>1</v>
@@ -5465,23 +5465,23 @@
       <c r="R79" s="17"/>
       <c r="S79" s="17"/>
       <c r="T79" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U79" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" s="10"/>
       <c r="B80" s="11"/>
       <c r="C80" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F80" s="13">
         <v>1</v>
@@ -5518,23 +5518,23 @@
       <c r="R80" s="17"/>
       <c r="S80" s="17"/>
       <c r="T80" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U80" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" s="10"/>
       <c r="B81" s="11"/>
       <c r="C81" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D81" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F81" s="13">
         <v>1</v>
@@ -5571,23 +5571,23 @@
       <c r="R81" s="17"/>
       <c r="S81" s="17"/>
       <c r="T81" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U81" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" s="10"/>
       <c r="B82" s="11"/>
       <c r="C82" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F82" s="13">
         <v>1</v>
@@ -5624,23 +5624,23 @@
       <c r="R82" s="17"/>
       <c r="S82" s="17"/>
       <c r="T82" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U82" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A83" s="10"/>
       <c r="B83" s="11"/>
       <c r="C83" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D83" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F83" s="13">
         <v>1</v>
@@ -5677,23 +5677,23 @@
       <c r="R83" s="17"/>
       <c r="S83" s="17"/>
       <c r="T83" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U83" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" s="10"/>
       <c r="B84" s="11"/>
       <c r="C84" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D84" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F84" s="13">
         <v>1</v>
@@ -5730,23 +5730,23 @@
       <c r="R84" s="17"/>
       <c r="S84" s="17"/>
       <c r="T84" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U84" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" s="10"/>
       <c r="B85" s="11"/>
       <c r="C85" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D85" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F85" s="13">
         <v>1</v>
@@ -5783,23 +5783,23 @@
       <c r="R85" s="17"/>
       <c r="S85" s="17"/>
       <c r="T85" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U85" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A86" s="10"/>
       <c r="B86" s="11"/>
       <c r="C86" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F86" s="13">
         <v>1</v>
@@ -5836,23 +5836,23 @@
       <c r="R86" s="17"/>
       <c r="S86" s="17"/>
       <c r="T86" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U86" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87" s="10"/>
       <c r="B87" s="11"/>
       <c r="C87" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D87" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F87" s="13">
         <v>1</v>
@@ -5889,23 +5889,23 @@
       <c r="R87" s="17"/>
       <c r="S87" s="17"/>
       <c r="T87" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U87" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
       <c r="B88" s="11"/>
       <c r="C88" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F88" s="13">
         <v>1</v>
@@ -5942,23 +5942,23 @@
       <c r="R88" s="17"/>
       <c r="S88" s="17"/>
       <c r="T88" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U88" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
       <c r="B89" s="11"/>
       <c r="C89" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F89" s="13">
         <v>1</v>
@@ -5995,23 +5995,23 @@
       <c r="R89" s="17"/>
       <c r="S89" s="17"/>
       <c r="T89" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U89" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="11"/>
       <c r="C90" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F90" s="13">
         <v>1</v>
@@ -6048,23 +6048,23 @@
       <c r="R90" s="17"/>
       <c r="S90" s="17"/>
       <c r="T90" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U90" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="11"/>
       <c r="C91" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F91" s="13">
         <v>1</v>
@@ -6101,23 +6101,23 @@
       <c r="R91" s="17"/>
       <c r="S91" s="17"/>
       <c r="T91" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U91" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="11"/>
       <c r="C92" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F92" s="13">
         <v>1</v>
@@ -6154,23 +6154,23 @@
       <c r="R92" s="17"/>
       <c r="S92" s="17"/>
       <c r="T92" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U92" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93" s="10"/>
       <c r="B93" s="11"/>
       <c r="C93" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F93" s="13">
         <v>1</v>
@@ -6207,23 +6207,23 @@
       <c r="R93" s="17"/>
       <c r="S93" s="17"/>
       <c r="T93" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U93" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="11"/>
       <c r="C94" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F94" s="13">
         <v>1</v>
@@ -6260,10 +6260,10 @@
       <c r="R94" s="17"/>
       <c r="S94" s="17"/>
       <c r="T94" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U94" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
